--- a/output/yearly_benthic_cover_iteration_33_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_33_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.30919925004898</v>
+        <v>44.98507645480532</v>
       </c>
       <c r="M2" t="n">
-        <v>99.2722618932147</v>
+        <v>101.7468766602641</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.96501169927016</v>
+        <v>88.07197311164784</v>
       </c>
       <c r="C3" t="n">
-        <v>45.89695366936363</v>
+        <v>45.91865077086596</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228594785648374</v>
+        <v>2.228852743868791</v>
       </c>
       <c r="E3" t="n">
-        <v>5.684827959572013</v>
+        <v>5.703176412915265</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428649285494581</v>
+        <v>0.7429509146229303</v>
       </c>
       <c r="G3" t="n">
-        <v>33.96275883651715</v>
+        <v>33.96914941417525</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17178671327507</v>
+        <v>34.17574207265479</v>
       </c>
       <c r="I3" t="n">
-        <v>6.531272672273989</v>
+        <v>6.608658337017507</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642905803434113</v>
+        <v>4.643443216393314</v>
       </c>
       <c r="K3" t="n">
-        <v>12.03498830072984</v>
+        <v>11.92802688835214</v>
       </c>
       <c r="L3" t="n">
-        <v>48.83360454507083</v>
+        <v>48.91611839430506</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7655465151643</v>
+        <v>106.7627960535232</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.99645511150831</v>
+        <v>87.30476432645212</v>
       </c>
       <c r="C4" t="n">
-        <v>42.55761112700765</v>
+        <v>42.79478991386114</v>
       </c>
       <c r="D4" t="n">
-        <v>2.181599042599592</v>
+        <v>2.192652989673623</v>
       </c>
       <c r="E4" t="n">
-        <v>6.473965398425006</v>
+        <v>6.530351940520037</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444173521839273</v>
+        <v>0.7445163931657938</v>
       </c>
       <c r="G4" t="n">
-        <v>33.24656534194952</v>
+        <v>33.41744187656663</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24319820046065</v>
+        <v>34.24775408562652</v>
       </c>
       <c r="I4" t="n">
-        <v>5.454101324740072</v>
+        <v>5.5188195836133</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652608451149546</v>
+        <v>4.653227457286212</v>
       </c>
       <c r="K4" t="n">
-        <v>13.00354488849169</v>
+        <v>12.69523567354788</v>
       </c>
       <c r="L4" t="n">
-        <v>44.25741974360417</v>
+        <v>44.32640056989603</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81857575910351</v>
+        <v>99.81642615730506</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.8389623636196</v>
+        <v>86.28591128610229</v>
       </c>
       <c r="C5" t="n">
-        <v>42.24656846014989</v>
+        <v>42.63261287952257</v>
       </c>
       <c r="D5" t="n">
-        <v>2.125085862444938</v>
+        <v>2.143448171859173</v>
       </c>
       <c r="E5" t="n">
-        <v>7.065114139856015</v>
+        <v>7.151672782199006</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457335462299256</v>
+        <v>0.7458414983390592</v>
       </c>
       <c r="G5" t="n">
-        <v>32.38533048622911</v>
+        <v>32.66752880454595</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30374312657657</v>
+        <v>34.30870892359673</v>
       </c>
       <c r="I5" t="n">
-        <v>4.553120538346004</v>
+        <v>4.607201740943256</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660834663937035</v>
+        <v>4.661509364619121</v>
       </c>
       <c r="K5" t="n">
-        <v>14.1610376363804</v>
+        <v>13.71408871389769</v>
       </c>
       <c r="L5" t="n">
-        <v>43.44089108889359</v>
+        <v>43.49999786259048</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84849718542388</v>
+        <v>99.84669945601075</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.37028777061367</v>
+        <v>85.12673226841035</v>
       </c>
       <c r="C6" t="n">
-        <v>41.48496729430209</v>
+        <v>42.18920136993781</v>
       </c>
       <c r="D6" t="n">
-        <v>2.053093931820451</v>
+        <v>2.08737553613707</v>
       </c>
       <c r="E6" t="n">
-        <v>7.459095192655893</v>
+        <v>7.605437492588749</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468531189705747</v>
+        <v>0.746964469778191</v>
       </c>
       <c r="G6" t="n">
-        <v>31.28820659734619</v>
+        <v>31.81294577023364</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35524347264643</v>
+        <v>34.36036560979679</v>
       </c>
       <c r="I6" t="n">
-        <v>3.799963463608047</v>
+        <v>3.845115453762237</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667831993566092</v>
+        <v>4.668527936113694</v>
       </c>
       <c r="K6" t="n">
-        <v>15.62971222938635</v>
+        <v>14.87326773158964</v>
       </c>
       <c r="L6" t="n">
-        <v>42.75884490580194</v>
+        <v>42.80955307233523</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87352442949037</v>
+        <v>99.87202217386266</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.78965072698016</v>
+        <v>83.71503298727012</v>
       </c>
       <c r="C7" t="n">
-        <v>40.49438450043852</v>
+        <v>41.37506780061993</v>
       </c>
       <c r="D7" t="n">
-        <v>1.976075019322389</v>
+        <v>2.018955353986627</v>
       </c>
       <c r="E7" t="n">
-        <v>7.707724253639936</v>
+        <v>7.890871830987534</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478065518741964</v>
+        <v>0.7479187102427672</v>
       </c>
       <c r="G7" t="n">
-        <v>30.11447381834686</v>
+        <v>30.77017818641415</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39910138621303</v>
+        <v>34.40426067116729</v>
       </c>
       <c r="I7" t="n">
-        <v>3.170678748370043</v>
+        <v>3.208356295454449</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673790949213728</v>
+        <v>4.674491939017296</v>
       </c>
       <c r="K7" t="n">
-        <v>17.21034927301983</v>
+        <v>16.28496701272989</v>
       </c>
       <c r="L7" t="n">
-        <v>42.18971168588589</v>
+        <v>42.23315642404567</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89444545934424</v>
+        <v>99.8931912373955</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.7063897667784</v>
+        <v>88.54492920173898</v>
       </c>
       <c r="C8" t="n">
-        <v>42.74180616225009</v>
+        <v>43.71201399028853</v>
       </c>
       <c r="D8" t="n">
-        <v>1.98036635603833</v>
+        <v>2.023196613341168</v>
       </c>
       <c r="E8" t="n">
-        <v>9.508904762111612</v>
+        <v>9.74338723565714</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494305234750213</v>
+        <v>0.749489877836934</v>
       </c>
       <c r="G8" t="n">
-        <v>30.59592462122667</v>
+        <v>31.28776695386328</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47380407985097</v>
+        <v>34.47653438049897</v>
       </c>
       <c r="I8" t="n">
-        <v>5.714018652356929</v>
+        <v>5.580242404060645</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683940771718883</v>
+        <v>4.684311736480838</v>
       </c>
       <c r="K8" t="n">
-        <v>12.29361023322159</v>
+        <v>11.45507079826103</v>
       </c>
       <c r="L8" t="n">
-        <v>44.77452904746053</v>
+        <v>44.64729706302251</v>
       </c>
       <c r="M8" t="n">
-        <v>99.8099454429322</v>
+        <v>99.81438185157208</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.71199176258263</v>
+        <v>86.6392181617645</v>
       </c>
       <c r="C9" t="n">
-        <v>41.63384196037209</v>
+        <v>42.67316330795469</v>
       </c>
       <c r="D9" t="n">
-        <v>1.890017671160878</v>
+        <v>1.937109729406099</v>
       </c>
       <c r="E9" t="n">
-        <v>9.870173589575474</v>
+        <v>10.10522951405302</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508209047864811</v>
+        <v>0.7508331979157756</v>
       </c>
       <c r="G9" t="n">
-        <v>29.20007099863365</v>
+        <v>29.95647451071479</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53776162017812</v>
+        <v>34.53832710412568</v>
       </c>
       <c r="I9" t="n">
-        <v>4.770516323332508</v>
+        <v>4.65853661857553</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692630654915508</v>
+        <v>4.692707486973599</v>
       </c>
       <c r="K9" t="n">
-        <v>14.28800823741737</v>
+        <v>13.36078183823551</v>
       </c>
       <c r="L9" t="n">
-        <v>43.9194270618673</v>
+        <v>43.81104812036367</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84127725965676</v>
+        <v>99.84499326655387</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.53567095727007</v>
+        <v>84.5332637936655</v>
       </c>
       <c r="C10" t="n">
-        <v>40.19733407041786</v>
+        <v>41.29071155879286</v>
       </c>
       <c r="D10" t="n">
-        <v>1.792439706180853</v>
+        <v>1.842797835093464</v>
       </c>
       <c r="E10" t="n">
-        <v>10.02422000731788</v>
+        <v>10.26124802838988</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520138397116342</v>
+        <v>0.7519843379844177</v>
       </c>
       <c r="G10" t="n">
-        <v>27.69252768367149</v>
+        <v>28.4979862200696</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59263662673516</v>
+        <v>34.59127954728322</v>
       </c>
       <c r="I10" t="n">
-        <v>3.981746595455323</v>
+        <v>3.888065712442312</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700086498197715</v>
+        <v>4.699902112402611</v>
       </c>
       <c r="K10" t="n">
-        <v>16.46432904272995</v>
+        <v>15.4667362063345</v>
       </c>
       <c r="L10" t="n">
-        <v>43.20582254453738</v>
+        <v>43.11314843991222</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86748565768519</v>
+        <v>99.87059620503959</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.31075429340108</v>
+        <v>82.16020189114629</v>
       </c>
       <c r="C11" t="n">
-        <v>38.58930493349278</v>
+        <v>39.52096364574624</v>
       </c>
       <c r="D11" t="n">
-        <v>1.693804445916371</v>
+        <v>1.737375887957154</v>
       </c>
       <c r="E11" t="n">
-        <v>10.02637590067413</v>
+        <v>10.21494709854319</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530381702420329</v>
+        <v>0.7529741430239962</v>
       </c>
       <c r="G11" t="n">
-        <v>26.16864954928211</v>
+        <v>26.86768628180692</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63975583113351</v>
+        <v>34.63681057910384</v>
       </c>
       <c r="I11" t="n">
-        <v>3.322641832140221</v>
+        <v>3.244319506811211</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706488564012707</v>
+        <v>4.706088393899978</v>
       </c>
       <c r="K11" t="n">
-        <v>18.68924570659894</v>
+        <v>17.83979810885371</v>
       </c>
       <c r="L11" t="n">
-        <v>42.61084528781231</v>
+        <v>42.53123642005443</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88939592790402</v>
+        <v>99.89199817465438</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.03842025938204</v>
+        <v>79.72812177237475</v>
       </c>
       <c r="C12" t="n">
-        <v>36.83101206433731</v>
+        <v>37.5915032240613</v>
       </c>
       <c r="D12" t="n">
-        <v>1.594082153191841</v>
+        <v>1.630371872576322</v>
       </c>
       <c r="E12" t="n">
-        <v>9.898093192333777</v>
+        <v>10.03692402334</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539185442300758</v>
+        <v>0.7538262239141733</v>
       </c>
       <c r="G12" t="n">
-        <v>24.62797716714811</v>
+        <v>25.21292041560956</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68025303458348</v>
+        <v>34.67600630005199</v>
       </c>
       <c r="I12" t="n">
-        <v>2.772105266456788</v>
+        <v>2.706659037419129</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711990901437975</v>
+        <v>4.711413899463585</v>
       </c>
       <c r="K12" t="n">
-        <v>20.96157974061797</v>
+        <v>20.27187822762523</v>
       </c>
       <c r="L12" t="n">
-        <v>42.1151125885964</v>
+        <v>42.04649856201316</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90770439355167</v>
+        <v>99.90988001369969</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.72170912094779</v>
+        <v>77.2341769400183</v>
       </c>
       <c r="C13" t="n">
-        <v>34.9423745388108</v>
+        <v>35.51602256939181</v>
       </c>
       <c r="D13" t="n">
-        <v>1.493338099881493</v>
+        <v>1.521602733287525</v>
       </c>
       <c r="E13" t="n">
-        <v>9.657947175363393</v>
+        <v>9.743608706852386</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546759863979126</v>
+        <v>0.7545607644135273</v>
       </c>
       <c r="G13" t="n">
-        <v>23.07151896348199</v>
+        <v>23.53085775328624</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71509537430397</v>
+        <v>34.70979516302227</v>
       </c>
       <c r="I13" t="n">
-        <v>2.312408606532089</v>
+        <v>2.257747041571801</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716724914986955</v>
+        <v>4.716004777584547</v>
       </c>
       <c r="K13" t="n">
-        <v>23.2782908790522</v>
+        <v>22.7658230599817</v>
       </c>
       <c r="L13" t="n">
-        <v>41.70233165806877</v>
+        <v>41.64296939736485</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92299707593176</v>
+        <v>99.92481502673836</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.5275203423229</v>
+        <v>84.00471844892617</v>
       </c>
       <c r="C14" t="n">
-        <v>38.97632996025787</v>
+        <v>39.60955014891949</v>
       </c>
       <c r="D14" t="n">
-        <v>1.495297847876904</v>
+        <v>1.523473502195521</v>
       </c>
       <c r="E14" t="n">
-        <v>11.9467088902979</v>
+        <v>12.04574722264505</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7556663681149834</v>
+        <v>0.7554884762179142</v>
       </c>
       <c r="G14" t="n">
-        <v>24.82980654640152</v>
+        <v>25.33353980549133</v>
       </c>
       <c r="H14" t="n">
-        <v>36.48866313760083</v>
+        <v>36.52622141275872</v>
       </c>
       <c r="I14" t="n">
-        <v>3.288462751312105</v>
+        <v>3.098445053255653</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722914800718647</v>
+        <v>4.721802976361965</v>
       </c>
       <c r="K14" t="n">
-        <v>16.47247965767708</v>
+        <v>15.99528155107384</v>
       </c>
       <c r="L14" t="n">
-        <v>44.44171861977706</v>
+        <v>44.29201362408175</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89052823771202</v>
+        <v>99.89684532407509</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.85731063706473</v>
+        <v>83.13945510978822</v>
       </c>
       <c r="C15" t="n">
-        <v>38.81400088511538</v>
+        <v>39.21661337633714</v>
       </c>
       <c r="D15" t="n">
-        <v>1.470733850793483</v>
+        <v>1.490343174014693</v>
       </c>
       <c r="E15" t="n">
-        <v>12.20768941364549</v>
+        <v>12.22129788511635</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7565003732792551</v>
+        <v>0.7562713861332114</v>
       </c>
       <c r="G15" t="n">
-        <v>24.42191503739299</v>
+        <v>24.78934096255346</v>
       </c>
       <c r="H15" t="n">
-        <v>36.52893452558127</v>
+        <v>36.57079223829529</v>
       </c>
       <c r="I15" t="n">
-        <v>2.743410103376907</v>
+        <v>2.584713300342641</v>
       </c>
       <c r="J15" t="n">
-        <v>4.728127332995346</v>
+        <v>4.726696163332573</v>
       </c>
       <c r="K15" t="n">
-        <v>17.14268936293526</v>
+        <v>16.86054489021177</v>
       </c>
       <c r="L15" t="n">
-        <v>43.9519635644129</v>
+        <v>43.83677381530509</v>
       </c>
       <c r="M15" t="n">
-        <v>99.90865381246353</v>
+        <v>99.913932081854</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.45310868413472</v>
+        <v>80.5693279773635</v>
       </c>
       <c r="C16" t="n">
-        <v>36.83366590320578</v>
+        <v>37.04611423377388</v>
       </c>
       <c r="D16" t="n">
-        <v>1.379234241145721</v>
+        <v>1.392096080613122</v>
       </c>
       <c r="E16" t="n">
-        <v>11.82959585886326</v>
+        <v>11.77494797006522</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7572176159384322</v>
+        <v>0.7569459219098723</v>
       </c>
       <c r="G16" t="n">
-        <v>22.90254041256426</v>
+        <v>23.15516653925559</v>
       </c>
       <c r="H16" t="n">
-        <v>36.56356783319282</v>
+        <v>36.60341056578708</v>
       </c>
       <c r="I16" t="n">
-        <v>2.288342622815018</v>
+        <v>2.155848887795891</v>
       </c>
       <c r="J16" t="n">
-        <v>4.732610099615203</v>
+        <v>4.730912011936703</v>
       </c>
       <c r="K16" t="n">
-        <v>19.54689131586527</v>
+        <v>19.43067202263653</v>
       </c>
       <c r="L16" t="n">
-        <v>43.54323694472404</v>
+        <v>43.45141615191339</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92379416379509</v>
+        <v>99.9282024083238</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.17738162953451</v>
+        <v>82.1926281713815</v>
       </c>
       <c r="C17" t="n">
-        <v>38.07152477072469</v>
+        <v>38.21768736711735</v>
       </c>
       <c r="D17" t="n">
-        <v>1.380535881578652</v>
+        <v>1.393328134645857</v>
       </c>
       <c r="E17" t="n">
-        <v>12.63668137957538</v>
+        <v>12.53699688379477</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7579322335400184</v>
+        <v>0.7576158456950471</v>
       </c>
       <c r="G17" t="n">
-        <v>23.33230494954552</v>
+        <v>23.56357050155347</v>
       </c>
       <c r="H17" t="n">
-        <v>37.00622484711207</v>
+        <v>37.02371669742287</v>
       </c>
       <c r="I17" t="n">
-        <v>2.326625878557754</v>
+        <v>2.18230107267543</v>
       </c>
       <c r="J17" t="n">
-        <v>4.737076459625117</v>
+        <v>4.735099035594046</v>
       </c>
       <c r="K17" t="n">
-        <v>17.82261837046547</v>
+        <v>17.80737182861852</v>
       </c>
       <c r="L17" t="n">
-        <v>44.02837578495385</v>
+        <v>43.90226175868858</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92251892614402</v>
+        <v>99.92732095442445</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.86149770007856</v>
+        <v>79.75415340609619</v>
       </c>
       <c r="C18" t="n">
-        <v>36.11471299791662</v>
+        <v>36.1161339716088</v>
       </c>
       <c r="D18" t="n">
-        <v>1.295983547558394</v>
+        <v>1.303701753447925</v>
       </c>
       <c r="E18" t="n">
-        <v>12.18613908624918</v>
+        <v>12.03387754443321</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7585460924706696</v>
+        <v>0.7581921317746922</v>
       </c>
       <c r="G18" t="n">
-        <v>21.90329403582658</v>
+        <v>22.04783454557685</v>
       </c>
       <c r="H18" t="n">
-        <v>37.03619665805616</v>
+        <v>37.0518790605396</v>
       </c>
       <c r="I18" t="n">
-        <v>1.940425201975901</v>
+        <v>1.819967546732106</v>
       </c>
       <c r="J18" t="n">
-        <v>4.740913077941687</v>
+        <v>4.738700823591828</v>
       </c>
       <c r="K18" t="n">
-        <v>20.13850229992144</v>
+        <v>20.24584659390379</v>
       </c>
       <c r="L18" t="n">
-        <v>43.68215620553531</v>
+        <v>43.57739996024644</v>
       </c>
       <c r="M18" t="n">
-        <v>99.93537150337337</v>
+        <v>99.93938052575902</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.93717241905316</v>
+        <v>78.74724350818957</v>
       </c>
       <c r="C19" t="n">
-        <v>35.48914098135383</v>
+        <v>35.38946934770547</v>
       </c>
       <c r="D19" t="n">
-        <v>1.262992735640072</v>
+        <v>1.267417923819124</v>
       </c>
       <c r="E19" t="n">
-        <v>12.14561398562441</v>
+        <v>11.95189367826227</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7590644047125061</v>
+        <v>0.758679193447846</v>
       </c>
       <c r="G19" t="n">
-        <v>21.34571947765488</v>
+        <v>21.43421270283561</v>
       </c>
       <c r="H19" t="n">
-        <v>37.06150337878081</v>
+        <v>37.07568114111049</v>
       </c>
       <c r="I19" t="n">
-        <v>1.618125907187301</v>
+        <v>1.517613909665188</v>
       </c>
       <c r="J19" t="n">
-        <v>4.744152529453165</v>
+        <v>4.741744959049039</v>
       </c>
       <c r="K19" t="n">
-        <v>21.06282758094685</v>
+        <v>21.25275649181044</v>
       </c>
       <c r="L19" t="n">
-        <v>43.39413073764442</v>
+        <v>43.30721950640818</v>
       </c>
       <c r="M19" t="n">
-        <v>99.9460992999451</v>
+        <v>99.9494453459241</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.48749591246244</v>
+        <v>76.19666297255633</v>
       </c>
       <c r="C20" t="n">
-        <v>33.28845380637271</v>
+        <v>33.07240267240735</v>
       </c>
       <c r="D20" t="n">
-        <v>1.174660335059585</v>
+        <v>1.174782947559099</v>
       </c>
       <c r="E20" t="n">
-        <v>11.5210342095831</v>
+        <v>11.28923181390835</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7595107318384535</v>
+        <v>0.7590991664379346</v>
       </c>
       <c r="G20" t="n">
-        <v>19.85282202039171</v>
+        <v>19.8675962398962</v>
       </c>
       <c r="H20" t="n">
-        <v>37.08329540878992</v>
+        <v>37.0962046836076</v>
       </c>
       <c r="I20" t="n">
-        <v>1.349231132809325</v>
+        <v>1.265378330910047</v>
       </c>
       <c r="J20" t="n">
-        <v>4.746942073990336</v>
+        <v>4.744369790237093</v>
       </c>
       <c r="K20" t="n">
-        <v>23.51250408753758</v>
+        <v>23.80333702744366</v>
       </c>
       <c r="L20" t="n">
-        <v>43.15409416422339</v>
+        <v>43.08210435821385</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95505205813369</v>
+        <v>99.95784405806486</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.22002874980701</v>
+        <v>82.27096182070335</v>
       </c>
       <c r="C21" t="n">
-        <v>36.70465694371391</v>
+        <v>36.78205205388228</v>
       </c>
       <c r="D21" t="n">
-        <v>1.17565715477884</v>
+        <v>1.175686836538097</v>
       </c>
       <c r="E21" t="n">
-        <v>13.40499731465738</v>
+        <v>13.30325899114187</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7601552545586693</v>
+        <v>0.7596832244308902</v>
       </c>
       <c r="G21" t="n">
-        <v>21.39499488405904</v>
+        <v>21.571723456375</v>
       </c>
       <c r="H21" t="n">
-        <v>38.64009009557754</v>
+        <v>38.81358775243606</v>
       </c>
       <c r="I21" t="n">
-        <v>2.093163705183848</v>
+        <v>1.899001407088372</v>
       </c>
       <c r="J21" t="n">
-        <v>4.750970340991685</v>
+        <v>4.748020152693066</v>
       </c>
       <c r="K21" t="n">
-        <v>17.77997125019299</v>
+        <v>17.72903817929667</v>
       </c>
       <c r="L21" t="n">
-        <v>45.44565884118462</v>
+        <v>45.42565838612153</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93028703509152</v>
+        <v>99.93674861930047</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_33_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_33_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>44.98507645480532</v>
+        <v>45.33160422098123</v>
       </c>
       <c r="M2" t="n">
-        <v>101.7468766602641</v>
+        <v>99.23212844620076</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.07197311164784</v>
+        <v>88.0160429449369</v>
       </c>
       <c r="C3" t="n">
-        <v>45.91865077086596</v>
+        <v>45.9211035038804</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228852743868791</v>
+        <v>2.228707461835455</v>
       </c>
       <c r="E3" t="n">
-        <v>5.703176412915265</v>
+        <v>5.701408278438853</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429509146229303</v>
+        <v>0.742902487278485</v>
       </c>
       <c r="G3" t="n">
-        <v>33.96914941417525</v>
+        <v>33.97060928695408</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17574207265479</v>
+        <v>34.1735144148103</v>
       </c>
       <c r="I3" t="n">
-        <v>6.608658337017507</v>
+        <v>6.555760470129201</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643443216393314</v>
+        <v>4.643140545490531</v>
       </c>
       <c r="K3" t="n">
-        <v>11.92802688835214</v>
+        <v>11.98395705506308</v>
       </c>
       <c r="L3" t="n">
-        <v>48.91611839430506</v>
+        <v>48.85961881392566</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7627960535232</v>
+        <v>106.7646793728692</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.30476432645212</v>
+        <v>87.14326898409419</v>
       </c>
       <c r="C4" t="n">
-        <v>42.79478991386114</v>
+        <v>42.68137584118208</v>
       </c>
       <c r="D4" t="n">
-        <v>2.192652989673623</v>
+        <v>2.186854349206</v>
       </c>
       <c r="E4" t="n">
-        <v>6.530351940520037</v>
+        <v>6.506769984488408</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445163931657938</v>
+        <v>0.7444581915421112</v>
       </c>
       <c r="G4" t="n">
-        <v>33.41744187656663</v>
+        <v>33.3326719349576</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24775408562652</v>
+        <v>34.24507681093711</v>
       </c>
       <c r="I4" t="n">
-        <v>5.5188195836133</v>
+        <v>5.474574015824751</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653227457286212</v>
+        <v>4.652863697138194</v>
       </c>
       <c r="K4" t="n">
-        <v>12.69523567354788</v>
+        <v>12.85673101590583</v>
       </c>
       <c r="L4" t="n">
-        <v>44.32640056989603</v>
+        <v>44.2797886854085</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81642615730506</v>
+        <v>99.8178955424964</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.28591128610229</v>
+        <v>85.9708581425477</v>
       </c>
       <c r="C5" t="n">
-        <v>42.63261287952257</v>
+        <v>42.35870112084554</v>
       </c>
       <c r="D5" t="n">
-        <v>2.143448171859173</v>
+        <v>2.12961452097535</v>
       </c>
       <c r="E5" t="n">
-        <v>7.151672782199006</v>
+        <v>7.098163367651301</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458414983390592</v>
+        <v>0.745777376753555</v>
       </c>
       <c r="G5" t="n">
-        <v>32.66752880454595</v>
+        <v>32.46020577518875</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30870892359673</v>
+        <v>34.30575933066353</v>
       </c>
       <c r="I5" t="n">
-        <v>4.607201740943256</v>
+        <v>4.570229166605488</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661509364619121</v>
+        <v>4.661108604709718</v>
       </c>
       <c r="K5" t="n">
-        <v>13.71408871389769</v>
+        <v>14.0291418574523</v>
       </c>
       <c r="L5" t="n">
-        <v>43.49999786259048</v>
+        <v>43.46008552126259</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84669945601075</v>
+        <v>99.84792849956044</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>85.12673226841035</v>
+        <v>84.67310599775391</v>
       </c>
       <c r="C6" t="n">
-        <v>42.18920136993781</v>
+        <v>41.7707629466926</v>
       </c>
       <c r="D6" t="n">
-        <v>2.08737553613707</v>
+        <v>2.066417544748385</v>
       </c>
       <c r="E6" t="n">
-        <v>7.605437492588749</v>
+        <v>7.52323032201338</v>
       </c>
       <c r="F6" t="n">
-        <v>0.746964469778191</v>
+        <v>0.7468972034563228</v>
       </c>
       <c r="G6" t="n">
-        <v>31.81294577023364</v>
+        <v>31.49693902785391</v>
       </c>
       <c r="H6" t="n">
-        <v>34.36036560979679</v>
+        <v>34.35727135899084</v>
       </c>
       <c r="I6" t="n">
-        <v>3.845115453762237</v>
+        <v>3.814243019089061</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668527936113694</v>
+        <v>4.668107521602017</v>
       </c>
       <c r="K6" t="n">
-        <v>14.87326773158964</v>
+        <v>15.32689400224608</v>
       </c>
       <c r="L6" t="n">
-        <v>42.80955307233523</v>
+        <v>42.77539224087782</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87202217386266</v>
+        <v>99.8730491898165</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.71503298727012</v>
+        <v>83.24887303828775</v>
       </c>
       <c r="C7" t="n">
-        <v>41.37506780061993</v>
+        <v>40.93900711347931</v>
       </c>
       <c r="D7" t="n">
-        <v>2.018955353986627</v>
+        <v>1.99732887816244</v>
       </c>
       <c r="E7" t="n">
-        <v>7.890871830987534</v>
+        <v>7.802129469002209</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479187102427672</v>
+        <v>0.7478489940534657</v>
       </c>
       <c r="G7" t="n">
-        <v>30.77017818641415</v>
+        <v>30.44386941735648</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40426067116729</v>
+        <v>34.40105372645942</v>
       </c>
       <c r="I7" t="n">
-        <v>3.208356295454449</v>
+        <v>3.182586340419576</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674491939017296</v>
+        <v>4.674056212834159</v>
       </c>
       <c r="K7" t="n">
-        <v>16.28496701272989</v>
+        <v>16.75112696171224</v>
       </c>
       <c r="L7" t="n">
-        <v>42.23315642404567</v>
+        <v>42.20391472983375</v>
       </c>
       <c r="M7" t="n">
-        <v>99.8931912373955</v>
+        <v>99.89404880502531</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.54492920173898</v>
+        <v>88.21732824603269</v>
       </c>
       <c r="C8" t="n">
-        <v>43.71201399028853</v>
+        <v>43.29910343441394</v>
       </c>
       <c r="D8" t="n">
-        <v>2.023196613341168</v>
+        <v>2.001605563813509</v>
       </c>
       <c r="E8" t="n">
-        <v>9.74338723565714</v>
+        <v>9.675566295567885</v>
       </c>
       <c r="F8" t="n">
-        <v>0.749489877836934</v>
+        <v>0.7494502902130531</v>
       </c>
       <c r="G8" t="n">
-        <v>31.28776695386328</v>
+        <v>30.96519343472464</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47653438049897</v>
+        <v>34.47471334980044</v>
       </c>
       <c r="I8" t="n">
-        <v>5.580242404060645</v>
+        <v>5.666734998081579</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684311736480838</v>
+        <v>4.684064313831581</v>
       </c>
       <c r="K8" t="n">
-        <v>11.45507079826103</v>
+        <v>11.78267175396731</v>
       </c>
       <c r="L8" t="n">
-        <v>44.64729706302251</v>
+        <v>44.72973723509213</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81438185157208</v>
+        <v>99.81151242347337</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.6392181617645</v>
+        <v>86.27399616176079</v>
       </c>
       <c r="C9" t="n">
-        <v>42.67316330795469</v>
+        <v>42.2355300275585</v>
       </c>
       <c r="D9" t="n">
-        <v>1.937109729406099</v>
+        <v>1.913878714062492</v>
       </c>
       <c r="E9" t="n">
-        <v>10.10522951405302</v>
+        <v>10.0399883909544</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508331979157756</v>
+        <v>0.750820182518328</v>
       </c>
       <c r="G9" t="n">
-        <v>29.95647451071479</v>
+        <v>29.60804349416205</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53832710412568</v>
+        <v>34.53772839584308</v>
       </c>
       <c r="I9" t="n">
-        <v>4.65853661857553</v>
+        <v>4.7309108434809</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692707486973599</v>
+        <v>4.692626140739549</v>
       </c>
       <c r="K9" t="n">
-        <v>13.36078183823551</v>
+        <v>13.72600383823923</v>
       </c>
       <c r="L9" t="n">
-        <v>43.81104812036367</v>
+        <v>43.8810568287</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84499326655387</v>
+        <v>99.84259069449772</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.5332637936655</v>
+        <v>84.0490452190698</v>
       </c>
       <c r="C10" t="n">
-        <v>41.29071155879286</v>
+        <v>40.74485078948975</v>
       </c>
       <c r="D10" t="n">
-        <v>1.842797835093464</v>
+        <v>1.814258923170924</v>
       </c>
       <c r="E10" t="n">
-        <v>10.26124802838988</v>
+        <v>10.1754943021874</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519843379844177</v>
+        <v>0.7519959595866752</v>
       </c>
       <c r="G10" t="n">
-        <v>28.4979862200696</v>
+        <v>28.06690764269735</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59127954728322</v>
+        <v>34.59181414098705</v>
       </c>
       <c r="I10" t="n">
-        <v>3.888065712442312</v>
+        <v>3.948599503023684</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699902112402611</v>
+        <v>4.699974747416718</v>
       </c>
       <c r="K10" t="n">
-        <v>15.4667362063345</v>
+        <v>15.95095478093021</v>
       </c>
       <c r="L10" t="n">
-        <v>43.11314843991222</v>
+        <v>43.17278023948338</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87059620503959</v>
+        <v>99.86858580990332</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.16020189114629</v>
+        <v>81.62829376351317</v>
       </c>
       <c r="C11" t="n">
-        <v>39.52096364574624</v>
+        <v>38.93632196972791</v>
       </c>
       <c r="D11" t="n">
-        <v>1.737375887957154</v>
+        <v>1.706911047858103</v>
       </c>
       <c r="E11" t="n">
-        <v>10.21494709854319</v>
+        <v>10.12257503339472</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529741430239962</v>
+        <v>0.7530077704194433</v>
       </c>
       <c r="G11" t="n">
-        <v>26.86768628180692</v>
+        <v>26.40621695320148</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63681057910384</v>
+        <v>34.63835743929438</v>
       </c>
       <c r="I11" t="n">
-        <v>3.244319506811211</v>
+        <v>3.294926954223527</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706088393899978</v>
+        <v>4.706298565121519</v>
       </c>
       <c r="K11" t="n">
-        <v>17.83979810885371</v>
+        <v>18.37170623648682</v>
       </c>
       <c r="L11" t="n">
-        <v>42.53123642005443</v>
+        <v>42.58228847425683</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89199817465438</v>
+        <v>99.89031668047157</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.72812177237475</v>
+        <v>79.1490185653996</v>
       </c>
       <c r="C12" t="n">
-        <v>37.5915032240613</v>
+        <v>36.96706435040234</v>
       </c>
       <c r="D12" t="n">
-        <v>1.630371872576322</v>
+        <v>1.598079687188068</v>
       </c>
       <c r="E12" t="n">
-        <v>10.03692402334</v>
+        <v>9.935325831605379</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538262239141733</v>
+        <v>0.7538795359856216</v>
       </c>
       <c r="G12" t="n">
-        <v>25.21292041560956</v>
+        <v>24.72257648185341</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67600630005199</v>
+        <v>34.67845865533858</v>
       </c>
       <c r="I12" t="n">
-        <v>2.706659037419129</v>
+        <v>2.748951273518416</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711413899463585</v>
+        <v>4.711747099910133</v>
       </c>
       <c r="K12" t="n">
-        <v>20.27187822762523</v>
+        <v>20.85098143460039</v>
       </c>
       <c r="L12" t="n">
-        <v>42.04649856201316</v>
+        <v>42.09042846626884</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90988001369969</v>
+        <v>99.90847425127157</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.2341769400183</v>
+        <v>76.61281256256045</v>
       </c>
       <c r="C13" t="n">
-        <v>35.51602256939181</v>
+        <v>34.85545432178197</v>
       </c>
       <c r="D13" t="n">
-        <v>1.521602733287525</v>
+        <v>1.487772460865987</v>
       </c>
       <c r="E13" t="n">
-        <v>9.743608706852386</v>
+        <v>9.631721064571233</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545607644135273</v>
+        <v>0.7546316750842608</v>
       </c>
       <c r="G13" t="n">
-        <v>23.53085775328624</v>
+        <v>23.01610410684485</v>
       </c>
       <c r="H13" t="n">
-        <v>34.70979516302227</v>
+        <v>34.71305705387598</v>
       </c>
       <c r="I13" t="n">
-        <v>2.257747041571801</v>
+        <v>2.293078232041503</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716004777584547</v>
+        <v>4.716447969276628</v>
       </c>
       <c r="K13" t="n">
-        <v>22.7658230599817</v>
+        <v>23.38718743743956</v>
       </c>
       <c r="L13" t="n">
-        <v>41.64296939736485</v>
+        <v>41.68099848318073</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92481502673836</v>
+        <v>99.92364024240226</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>84.00471844892617</v>
+        <v>83.49523066033024</v>
       </c>
       <c r="C14" t="n">
-        <v>39.60955014891949</v>
+        <v>39.11883341233538</v>
       </c>
       <c r="D14" t="n">
-        <v>1.523473502195521</v>
+        <v>1.489545551779203</v>
       </c>
       <c r="E14" t="n">
-        <v>12.04574722264505</v>
+        <v>12.00879068675481</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554884762179142</v>
+        <v>0.7555310266995862</v>
       </c>
       <c r="G14" t="n">
-        <v>25.33353980549133</v>
+        <v>24.91158701815798</v>
       </c>
       <c r="H14" t="n">
-        <v>36.52622141275872</v>
+        <v>36.62248010827431</v>
       </c>
       <c r="I14" t="n">
-        <v>3.098445053255653</v>
+        <v>2.985227351791928</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721802976361965</v>
+        <v>4.722068916872412</v>
       </c>
       <c r="K14" t="n">
-        <v>15.99528155107384</v>
+        <v>16.50476933966976</v>
       </c>
       <c r="L14" t="n">
-        <v>44.29201362408175</v>
+        <v>44.27700811914021</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89684532407509</v>
+        <v>99.90061087114535</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.13945510978822</v>
+        <v>82.63408084407311</v>
       </c>
       <c r="C15" t="n">
-        <v>39.21661337633714</v>
+        <v>38.71891937710554</v>
       </c>
       <c r="D15" t="n">
-        <v>1.490343174014693</v>
+        <v>1.457612674933362</v>
       </c>
       <c r="E15" t="n">
-        <v>12.22129788511635</v>
+        <v>12.16637762997631</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562713861332114</v>
+        <v>0.7562899607635731</v>
       </c>
       <c r="G15" t="n">
-        <v>24.78934096255346</v>
+        <v>24.37753242725602</v>
       </c>
       <c r="H15" t="n">
-        <v>36.57079223829529</v>
+        <v>36.65926754211839</v>
       </c>
       <c r="I15" t="n">
-        <v>2.584713300342641</v>
+        <v>2.490188354253128</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726696163332573</v>
+        <v>4.726812254772331</v>
       </c>
       <c r="K15" t="n">
-        <v>16.86054489021177</v>
+        <v>17.3659191559269</v>
       </c>
       <c r="L15" t="n">
-        <v>43.83677381530509</v>
+        <v>43.83223848497332</v>
       </c>
       <c r="M15" t="n">
-        <v>99.913932081854</v>
+        <v>99.91707701800576</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.5693279773635</v>
+        <v>80.0450354333875</v>
       </c>
       <c r="C16" t="n">
-        <v>37.04611423377388</v>
+        <v>36.51462677588994</v>
       </c>
       <c r="D16" t="n">
-        <v>1.392096080613122</v>
+        <v>1.359480270995262</v>
       </c>
       <c r="E16" t="n">
-        <v>11.77494797006522</v>
+        <v>11.69344631700967</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569459219098723</v>
+        <v>0.7569440832733376</v>
       </c>
       <c r="G16" t="n">
-        <v>23.15516653925559</v>
+        <v>22.73633795885927</v>
       </c>
       <c r="H16" t="n">
-        <v>36.60341056578708</v>
+        <v>36.69097449756516</v>
       </c>
       <c r="I16" t="n">
-        <v>2.155848887795891</v>
+        <v>2.07695178522643</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730912011936703</v>
+        <v>4.730900520458359</v>
       </c>
       <c r="K16" t="n">
-        <v>19.43067202263653</v>
+        <v>19.9549645666125</v>
       </c>
       <c r="L16" t="n">
-        <v>43.45141615191339</v>
+        <v>43.46123675876833</v>
       </c>
       <c r="M16" t="n">
-        <v>99.9282024083238</v>
+        <v>99.93082810127076</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.1926281713815</v>
+        <v>81.73564425000868</v>
       </c>
       <c r="C17" t="n">
-        <v>38.21768736711735</v>
+        <v>37.74443684594252</v>
       </c>
       <c r="D17" t="n">
-        <v>1.393328134645857</v>
+        <v>1.360631067082429</v>
       </c>
       <c r="E17" t="n">
-        <v>12.53699688379477</v>
+        <v>12.47593850307885</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7576158456950471</v>
+        <v>0.7575848342337008</v>
       </c>
       <c r="G17" t="n">
-        <v>23.56357050155347</v>
+        <v>23.18223299733077</v>
       </c>
       <c r="H17" t="n">
-        <v>37.02371669742287</v>
+        <v>37.14868209519563</v>
       </c>
       <c r="I17" t="n">
-        <v>2.18230107267543</v>
+        <v>2.075669539126678</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735099035594046</v>
+        <v>4.734905213960629</v>
       </c>
       <c r="K17" t="n">
-        <v>17.80737182861852</v>
+        <v>18.26435574999132</v>
       </c>
       <c r="L17" t="n">
-        <v>43.90226175868858</v>
+        <v>43.9220769381665</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92732095442445</v>
+        <v>99.93086953410034</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.75415340609619</v>
+        <v>79.24698254208231</v>
       </c>
       <c r="C18" t="n">
-        <v>36.1161339716088</v>
+        <v>35.57601312978919</v>
       </c>
       <c r="D18" t="n">
-        <v>1.303701753447925</v>
+        <v>1.270084042505859</v>
       </c>
       <c r="E18" t="n">
-        <v>12.03387754443321</v>
+        <v>11.93418939237165</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7581921317746922</v>
+        <v>0.7581364292605675</v>
       </c>
       <c r="G18" t="n">
-        <v>22.04783454557685</v>
+        <v>21.63950604383698</v>
       </c>
       <c r="H18" t="n">
-        <v>37.0518790605396</v>
+        <v>37.17572992848428</v>
       </c>
       <c r="I18" t="n">
-        <v>1.819967546732106</v>
+        <v>1.730984022744429</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738700823591828</v>
+        <v>4.738352682878546</v>
       </c>
       <c r="K18" t="n">
-        <v>20.24584659390379</v>
+        <v>20.75301745791769</v>
       </c>
       <c r="L18" t="n">
-        <v>43.57739996024644</v>
+        <v>43.61331192509516</v>
       </c>
       <c r="M18" t="n">
-        <v>99.93938052575902</v>
+        <v>99.94234251280204</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.74724350818957</v>
+        <v>78.20685030186392</v>
       </c>
       <c r="C19" t="n">
-        <v>35.38946934770547</v>
+        <v>34.80219811536009</v>
       </c>
       <c r="D19" t="n">
-        <v>1.267417923819124</v>
+        <v>1.232928403299774</v>
       </c>
       <c r="E19" t="n">
-        <v>11.95189367826227</v>
+        <v>11.82562332156244</v>
       </c>
       <c r="F19" t="n">
-        <v>0.758679193447846</v>
+        <v>0.7586028310652095</v>
       </c>
       <c r="G19" t="n">
-        <v>21.43421270283561</v>
+        <v>21.00645370064214</v>
       </c>
       <c r="H19" t="n">
-        <v>37.07568114111049</v>
+        <v>37.19860025479803</v>
       </c>
       <c r="I19" t="n">
-        <v>1.517613909665188</v>
+        <v>1.443374096338771</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741744959049039</v>
+        <v>4.741267694157559</v>
       </c>
       <c r="K19" t="n">
-        <v>21.25275649181044</v>
+        <v>21.79314969813606</v>
       </c>
       <c r="L19" t="n">
-        <v>43.30721950640818</v>
+        <v>43.35656929698318</v>
       </c>
       <c r="M19" t="n">
-        <v>99.9494453459241</v>
+        <v>99.95191711047934</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.19666297255633</v>
+        <v>75.51868764295757</v>
       </c>
       <c r="C20" t="n">
-        <v>33.07240267240735</v>
+        <v>32.3359142221547</v>
       </c>
       <c r="D20" t="n">
-        <v>1.174782947559099</v>
+        <v>1.136237895627696</v>
       </c>
       <c r="E20" t="n">
-        <v>11.28923181390835</v>
+        <v>11.09879217109438</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7590991664379346</v>
+        <v>0.7590057958216653</v>
       </c>
       <c r="G20" t="n">
-        <v>19.8675962398962</v>
+        <v>19.35905498124446</v>
       </c>
       <c r="H20" t="n">
-        <v>37.0962046836076</v>
+        <v>37.21835990276971</v>
       </c>
       <c r="I20" t="n">
-        <v>1.265378330910047</v>
+        <v>1.203450672514269</v>
       </c>
       <c r="J20" t="n">
-        <v>4.744369790237093</v>
+        <v>4.743786223885407</v>
       </c>
       <c r="K20" t="n">
-        <v>23.80333702744366</v>
+        <v>24.48131235704242</v>
       </c>
       <c r="L20" t="n">
-        <v>43.08210435821385</v>
+        <v>43.14267969590456</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95784405806486</v>
+        <v>99.95990627510167</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.27096182070335</v>
+        <v>81.61712766715202</v>
       </c>
       <c r="C21" t="n">
-        <v>36.78205205388228</v>
+        <v>36.1303417906137</v>
       </c>
       <c r="D21" t="n">
-        <v>1.175686836538097</v>
+        <v>1.137037611569071</v>
       </c>
       <c r="E21" t="n">
-        <v>13.30325899114187</v>
+        <v>13.14016958211364</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7596832244308902</v>
+        <v>0.7595400052833016</v>
       </c>
       <c r="G21" t="n">
-        <v>21.571723456375</v>
+        <v>21.11902413453517</v>
       </c>
       <c r="H21" t="n">
-        <v>38.81358775243606</v>
+        <v>38.99089893328647</v>
       </c>
       <c r="I21" t="n">
-        <v>1.899001407088372</v>
+        <v>1.723332367343724</v>
       </c>
       <c r="J21" t="n">
-        <v>4.748020152693066</v>
+        <v>4.747125033020634</v>
       </c>
       <c r="K21" t="n">
-        <v>17.72903817929667</v>
+        <v>18.382872332848</v>
       </c>
       <c r="L21" t="n">
-        <v>45.42565838612153</v>
+        <v>45.42938186683759</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93674861930047</v>
+        <v>99.94259599029928</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_33_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_33_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.33160422098123</v>
+        <v>43.58788120479296</v>
       </c>
       <c r="M2" t="n">
-        <v>99.23212844620076</v>
+        <v>94.72061441823277</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.0160429449369</v>
+        <v>81.5716487997168</v>
       </c>
       <c r="C3" t="n">
-        <v>45.9211035038804</v>
+        <v>43.32720435527235</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228707461835455</v>
+        <v>2.185586542148304</v>
       </c>
       <c r="E3" t="n">
-        <v>5.701408278438853</v>
+        <v>4.154935749611107</v>
       </c>
       <c r="F3" t="n">
-        <v>0.742902487278485</v>
+        <v>0.7376997782840633</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97060928695408</v>
+        <v>32.87486423814742</v>
       </c>
       <c r="H3" t="n">
-        <v>34.1735144148103</v>
+        <v>33.93418980106691</v>
       </c>
       <c r="I3" t="n">
-        <v>6.555760470129201</v>
+        <v>3.073749076183597</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643140545490531</v>
+        <v>4.610623614275395</v>
       </c>
       <c r="K3" t="n">
-        <v>11.98395705506308</v>
+        <v>18.42835120028321</v>
       </c>
       <c r="L3" t="n">
-        <v>48.85961881392566</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7646793728692</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.14326898409419</v>
+        <v>88.76048219285163</v>
       </c>
       <c r="C4" t="n">
-        <v>42.68137584118208</v>
+        <v>42.95592914876478</v>
       </c>
       <c r="D4" t="n">
-        <v>2.186854349206</v>
+        <v>2.191368235586365</v>
       </c>
       <c r="E4" t="n">
-        <v>6.506769984488408</v>
+        <v>6.564459190490075</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444581915421112</v>
+        <v>0.7396512699706709</v>
       </c>
       <c r="G4" t="n">
-        <v>33.3326719349576</v>
+        <v>33.57408494345766</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24507681093711</v>
+        <v>34.02395841865086</v>
       </c>
       <c r="I4" t="n">
-        <v>5.474574015824751</v>
+        <v>7.044139697379305</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652863697138194</v>
+        <v>4.622820437316693</v>
       </c>
       <c r="K4" t="n">
-        <v>12.85673101590583</v>
+        <v>11.23951780714838</v>
       </c>
       <c r="L4" t="n">
-        <v>44.2797886854085</v>
+        <v>45.5703678947725</v>
       </c>
       <c r="M4" t="n">
-        <v>99.8178955424964</v>
+        <v>99.76581485068566</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.9708581425477</v>
+        <v>87.75986686163318</v>
       </c>
       <c r="C5" t="n">
-        <v>42.35870112084554</v>
+        <v>43.04730104403345</v>
       </c>
       <c r="D5" t="n">
-        <v>2.12961452097535</v>
+        <v>2.144348661025692</v>
       </c>
       <c r="E5" t="n">
-        <v>7.098163367651301</v>
+        <v>7.404146386184437</v>
       </c>
       <c r="F5" t="n">
-        <v>0.745777376753555</v>
+        <v>0.7413040912696313</v>
       </c>
       <c r="G5" t="n">
-        <v>32.46020577518875</v>
+        <v>32.85369520490564</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30575933066353</v>
+        <v>34.09998819840303</v>
       </c>
       <c r="I5" t="n">
-        <v>4.570229166605488</v>
+        <v>5.883233749409548</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661108604709718</v>
+        <v>4.633150570435196</v>
       </c>
       <c r="K5" t="n">
-        <v>14.0291418574523</v>
+        <v>12.24013313836682</v>
       </c>
       <c r="L5" t="n">
-        <v>43.46008552126259</v>
+        <v>44.5168952704503</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84792849956044</v>
+        <v>99.80432945285058</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.67310599775391</v>
+        <v>86.54864673688157</v>
       </c>
       <c r="C6" t="n">
-        <v>41.7707629466926</v>
+        <v>42.7493900171629</v>
       </c>
       <c r="D6" t="n">
-        <v>2.066417544748385</v>
+        <v>2.087036052442936</v>
       </c>
       <c r="E6" t="n">
-        <v>7.52323032201338</v>
+        <v>8.024915301728033</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468972034563228</v>
+        <v>0.7427064868632469</v>
       </c>
       <c r="G6" t="n">
-        <v>31.49693902785391</v>
+        <v>31.97560527111882</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35727135899084</v>
+        <v>34.16449839570935</v>
       </c>
       <c r="I6" t="n">
-        <v>3.814243019089061</v>
+        <v>4.911969686123888</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668107521602017</v>
+        <v>4.641915542895294</v>
       </c>
       <c r="K6" t="n">
-        <v>15.32689400224608</v>
+        <v>13.45135326311844</v>
       </c>
       <c r="L6" t="n">
-        <v>42.77539224087782</v>
+        <v>43.63583356001286</v>
       </c>
       <c r="M6" t="n">
-        <v>99.8730491898165</v>
+        <v>99.83657684029419</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.24887303828775</v>
+        <v>85.23597944545151</v>
       </c>
       <c r="C7" t="n">
-        <v>40.93900711347931</v>
+        <v>42.19981383268463</v>
       </c>
       <c r="D7" t="n">
-        <v>1.99732887816244</v>
+        <v>2.025185425650699</v>
       </c>
       <c r="E7" t="n">
-        <v>7.802129469002209</v>
+        <v>8.470403726949467</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478489940534657</v>
+        <v>0.7438972988645564</v>
       </c>
       <c r="G7" t="n">
-        <v>30.44386941735648</v>
+        <v>31.02798808656424</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40105372645942</v>
+        <v>34.21927574776959</v>
       </c>
       <c r="I7" t="n">
-        <v>3.182586340419576</v>
+        <v>4.099871041749483</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674056212834159</v>
+        <v>4.649358117903478</v>
       </c>
       <c r="K7" t="n">
-        <v>16.75112696171224</v>
+        <v>14.76402055454849</v>
       </c>
       <c r="L7" t="n">
-        <v>42.20391472983375</v>
+        <v>42.89972201037455</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89404880502531</v>
+        <v>99.86355639760767</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.21732824603269</v>
+        <v>83.59857312851042</v>
       </c>
       <c r="C8" t="n">
-        <v>43.29910343441394</v>
+        <v>41.1994947546642</v>
       </c>
       <c r="D8" t="n">
-        <v>2.001605563813509</v>
+        <v>1.947979651382542</v>
       </c>
       <c r="E8" t="n">
-        <v>9.675566295567885</v>
+        <v>8.717691386537505</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494502902130531</v>
+        <v>0.7449120834227341</v>
       </c>
       <c r="G8" t="n">
-        <v>30.96519343472464</v>
+        <v>29.84511376114951</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47471334980044</v>
+        <v>34.26595583744576</v>
       </c>
       <c r="I8" t="n">
-        <v>5.666734998081579</v>
+        <v>3.421219887180289</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684064313831581</v>
+        <v>4.655700521392089</v>
       </c>
       <c r="K8" t="n">
-        <v>11.78267175396731</v>
+        <v>16.40142687148958</v>
       </c>
       <c r="L8" t="n">
-        <v>44.72973723509213</v>
+        <v>42.28519306713096</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81151242347337</v>
+        <v>99.88611469328474</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.27399616176079</v>
+        <v>81.8358668813753</v>
       </c>
       <c r="C9" t="n">
-        <v>42.2355300275585</v>
+        <v>39.96816006413221</v>
       </c>
       <c r="D9" t="n">
-        <v>1.913878714062492</v>
+        <v>1.865385337695608</v>
       </c>
       <c r="E9" t="n">
-        <v>10.0399883909544</v>
+        <v>8.823783249398748</v>
       </c>
       <c r="F9" t="n">
-        <v>0.750820182518328</v>
+        <v>0.7457781363761866</v>
       </c>
       <c r="G9" t="n">
-        <v>29.60804349416205</v>
+        <v>28.57968129820715</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53772839584308</v>
+        <v>34.30579427330457</v>
       </c>
       <c r="I9" t="n">
-        <v>4.7309108434809</v>
+        <v>2.854331234041878</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692626140739549</v>
+        <v>4.661113352351167</v>
       </c>
       <c r="K9" t="n">
-        <v>13.72600383823923</v>
+        <v>18.16413311862469</v>
       </c>
       <c r="L9" t="n">
-        <v>43.8810568287</v>
+        <v>41.77267293148809</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84259069449772</v>
+        <v>99.90496611424498</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.0490452190698</v>
+        <v>86.29420318261495</v>
       </c>
       <c r="C10" t="n">
-        <v>40.74485078948975</v>
+        <v>43.00555229014022</v>
       </c>
       <c r="D10" t="n">
-        <v>1.814258923170924</v>
+        <v>1.867531471550915</v>
       </c>
       <c r="E10" t="n">
-        <v>10.1754943021874</v>
+        <v>10.57932234976277</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519959595866752</v>
+        <v>0.7466361573301853</v>
       </c>
       <c r="G10" t="n">
-        <v>28.06690764269735</v>
+        <v>29.86154038440221</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59181414098705</v>
+        <v>35.5942412771094</v>
       </c>
       <c r="I10" t="n">
-        <v>3.948599503023684</v>
+        <v>2.978455559145797</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699974747416718</v>
+        <v>4.666475983313659</v>
       </c>
       <c r="K10" t="n">
-        <v>15.95095478093021</v>
+        <v>13.70579681738506</v>
       </c>
       <c r="L10" t="n">
-        <v>43.17278023948338</v>
+        <v>43.18948313343655</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86858580990332</v>
+        <v>99.90083224096183</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.62829376351317</v>
+        <v>86.05015052081622</v>
       </c>
       <c r="C11" t="n">
-        <v>38.93632196972791</v>
+        <v>43.12587708439932</v>
       </c>
       <c r="D11" t="n">
-        <v>1.706911047858103</v>
+        <v>1.850248419343218</v>
       </c>
       <c r="E11" t="n">
-        <v>10.12257503339472</v>
+        <v>10.94523478065153</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530077704194433</v>
+        <v>0.7473711317765743</v>
       </c>
       <c r="G11" t="n">
-        <v>26.40621695320148</v>
+        <v>29.62547504659202</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63835743929438</v>
+        <v>35.66956757501948</v>
       </c>
       <c r="I11" t="n">
-        <v>3.294926954223527</v>
+        <v>2.54118399382981</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706298565121519</v>
+        <v>4.671069573603591</v>
       </c>
       <c r="K11" t="n">
-        <v>18.37170623648682</v>
+        <v>13.94984947918378</v>
       </c>
       <c r="L11" t="n">
-        <v>42.58228847425683</v>
+        <v>42.83965060439716</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89031668047157</v>
+        <v>99.91537716798027</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.1490185653996</v>
+        <v>84.22499318132802</v>
       </c>
       <c r="C12" t="n">
-        <v>36.96706435040234</v>
+        <v>41.69611426024039</v>
       </c>
       <c r="D12" t="n">
-        <v>1.598079687188068</v>
+        <v>1.772126881081524</v>
       </c>
       <c r="E12" t="n">
-        <v>9.935325831605379</v>
+        <v>10.83634127842386</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538795359856216</v>
+        <v>0.7479980242803184</v>
       </c>
       <c r="G12" t="n">
-        <v>24.72257648185341</v>
+        <v>28.37462264311057</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67845865533858</v>
+        <v>35.6994870936814</v>
       </c>
       <c r="I12" t="n">
-        <v>2.748951273518416</v>
+        <v>2.119429608998363</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711747099910133</v>
+        <v>4.674987651751991</v>
       </c>
       <c r="K12" t="n">
-        <v>20.85098143460039</v>
+        <v>15.77500681867198</v>
       </c>
       <c r="L12" t="n">
-        <v>42.09042846626884</v>
+        <v>42.45829047681458</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90847425127157</v>
+        <v>99.92941155572694</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.61281256256045</v>
+        <v>85.31987749101224</v>
       </c>
       <c r="C13" t="n">
-        <v>34.85545432178197</v>
+        <v>42.62294433963439</v>
       </c>
       <c r="D13" t="n">
-        <v>1.487772460865987</v>
+        <v>1.773495525643332</v>
       </c>
       <c r="E13" t="n">
-        <v>9.631721064571233</v>
+        <v>11.45571760966438</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546316750842608</v>
+        <v>0.7485757162272687</v>
       </c>
       <c r="G13" t="n">
-        <v>23.01610410684485</v>
+        <v>28.67807393293623</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71305705387598</v>
+        <v>36.00859550433925</v>
       </c>
       <c r="I13" t="n">
-        <v>2.293078232041503</v>
+        <v>1.976820975781341</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716447969276628</v>
+        <v>4.678598226420431</v>
       </c>
       <c r="K13" t="n">
-        <v>23.38718743743956</v>
+        <v>14.68012250898777</v>
       </c>
       <c r="L13" t="n">
-        <v>41.68099848318073</v>
+        <v>42.63108997069098</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92364024240226</v>
+        <v>99.93415681931315</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.49523066033024</v>
+        <v>83.41434446697734</v>
       </c>
       <c r="C14" t="n">
-        <v>39.11883341233538</v>
+        <v>41.02488822929485</v>
       </c>
       <c r="D14" t="n">
-        <v>1.489545551779203</v>
+        <v>1.693969457434458</v>
       </c>
       <c r="E14" t="n">
-        <v>12.00879068675481</v>
+        <v>11.21676622712419</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555310266995862</v>
+        <v>0.7490688285137479</v>
       </c>
       <c r="G14" t="n">
-        <v>24.91158701815798</v>
+        <v>27.39210820552762</v>
       </c>
       <c r="H14" t="n">
-        <v>36.62248010827431</v>
+        <v>36.03231559100134</v>
       </c>
       <c r="I14" t="n">
-        <v>2.985227351791928</v>
+        <v>1.648435979165051</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722068916872412</v>
+        <v>4.681680178210925</v>
       </c>
       <c r="K14" t="n">
-        <v>16.50476933966976</v>
+        <v>16.58565553302266</v>
       </c>
       <c r="L14" t="n">
-        <v>44.27700811914021</v>
+        <v>42.3345445439108</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90061087114535</v>
+        <v>99.9450883062283</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.63408084407311</v>
+        <v>82.56546649702329</v>
       </c>
       <c r="C15" t="n">
-        <v>38.71891937710554</v>
+        <v>40.40656319693367</v>
       </c>
       <c r="D15" t="n">
-        <v>1.457612674933362</v>
+        <v>1.657985417433744</v>
       </c>
       <c r="E15" t="n">
-        <v>12.16637762997631</v>
+        <v>11.2116760111544</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562899607635731</v>
+        <v>0.7494919322730919</v>
       </c>
       <c r="G15" t="n">
-        <v>24.37753242725602</v>
+        <v>26.8102330642459</v>
       </c>
       <c r="H15" t="n">
-        <v>36.65926754211839</v>
+        <v>36.05266807077903</v>
       </c>
       <c r="I15" t="n">
-        <v>2.490188354253128</v>
+        <v>1.399087424430304</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726812254772331</v>
+        <v>4.684324576706825</v>
       </c>
       <c r="K15" t="n">
-        <v>17.3659191559269</v>
+        <v>17.4345335029767</v>
       </c>
       <c r="L15" t="n">
-        <v>43.83223848497332</v>
+        <v>42.11229337973873</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91707701800576</v>
+        <v>99.95339007964911</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.0450354333875</v>
+        <v>80.32925139376695</v>
       </c>
       <c r="C16" t="n">
-        <v>36.51462677588994</v>
+        <v>38.38748901968833</v>
       </c>
       <c r="D16" t="n">
-        <v>1.359480270995262</v>
+        <v>1.565304664999247</v>
       </c>
       <c r="E16" t="n">
-        <v>11.69344631700967</v>
+        <v>10.77935935340854</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569440832733376</v>
+        <v>0.7498547142964932</v>
       </c>
       <c r="G16" t="n">
-        <v>22.73633795885927</v>
+        <v>25.31155126209559</v>
       </c>
       <c r="H16" t="n">
-        <v>36.69097449756516</v>
+        <v>36.07011890554928</v>
       </c>
       <c r="I16" t="n">
-        <v>2.07695178522643</v>
+        <v>1.166470529064723</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730900520458359</v>
+        <v>4.686591964353084</v>
       </c>
       <c r="K16" t="n">
-        <v>19.9549645666125</v>
+        <v>19.67074860623305</v>
       </c>
       <c r="L16" t="n">
-        <v>43.46123675876833</v>
+        <v>41.90289883451111</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93082810127076</v>
+        <v>99.96113646043248</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.73564425000868</v>
+        <v>84.83622930199209</v>
       </c>
       <c r="C17" t="n">
-        <v>37.74443684594252</v>
+        <v>41.34668077521717</v>
       </c>
       <c r="D17" t="n">
-        <v>1.360631067082429</v>
+        <v>1.566122455356819</v>
       </c>
       <c r="E17" t="n">
-        <v>12.47593850307885</v>
+        <v>12.36687086173146</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575848342337008</v>
+        <v>0.7502464744238625</v>
       </c>
       <c r="G17" t="n">
-        <v>23.18223299733077</v>
+        <v>26.68504247612479</v>
       </c>
       <c r="H17" t="n">
-        <v>37.14868209519563</v>
+        <v>37.44923091217998</v>
       </c>
       <c r="I17" t="n">
-        <v>2.075669539126678</v>
+        <v>1.32967565702603</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734905213960629</v>
+        <v>4.689040465149142</v>
       </c>
       <c r="K17" t="n">
-        <v>18.26435574999132</v>
+        <v>15.16377069800792</v>
       </c>
       <c r="L17" t="n">
-        <v>43.9220769381665</v>
+        <v>43.44524914899722</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93086953410034</v>
+        <v>99.95570062222232</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.24698254208231</v>
+        <v>86.43562393941167</v>
       </c>
       <c r="C18" t="n">
-        <v>35.57601312978919</v>
+        <v>42.09219636792005</v>
       </c>
       <c r="D18" t="n">
-        <v>1.270084042505859</v>
+        <v>1.567412391368229</v>
       </c>
       <c r="E18" t="n">
-        <v>11.93418939237165</v>
+        <v>12.97871816406447</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7581364292605675</v>
+        <v>0.750864414573742</v>
       </c>
       <c r="G18" t="n">
-        <v>21.63950604383698</v>
+        <v>26.82987061532289</v>
       </c>
       <c r="H18" t="n">
-        <v>37.17572992848428</v>
+        <v>37.48007595331198</v>
       </c>
       <c r="I18" t="n">
-        <v>1.730984022744429</v>
+        <v>2.135779809684485</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738352682878546</v>
+        <v>4.692902591085889</v>
       </c>
       <c r="K18" t="n">
-        <v>20.75301745791769</v>
+        <v>13.56437606058831</v>
       </c>
       <c r="L18" t="n">
-        <v>43.61331192509516</v>
+        <v>44.2722935007122</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94234251280204</v>
+        <v>99.92886592922058</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.20685030186392</v>
+        <v>83.94863120258253</v>
       </c>
       <c r="C19" t="n">
-        <v>34.80219811536009</v>
+        <v>39.93650893317859</v>
       </c>
       <c r="D19" t="n">
-        <v>1.232928403299774</v>
+        <v>1.474241588052673</v>
       </c>
       <c r="E19" t="n">
-        <v>11.82562332156244</v>
+        <v>12.50407747007038</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7586028310652095</v>
+        <v>0.7513954321635449</v>
       </c>
       <c r="G19" t="n">
-        <v>21.00645370064214</v>
+        <v>25.23503787580374</v>
       </c>
       <c r="H19" t="n">
-        <v>37.19860025479803</v>
+        <v>37.50658217628921</v>
       </c>
       <c r="I19" t="n">
-        <v>1.443374096338771</v>
+        <v>1.781075209180835</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741267694157559</v>
+        <v>4.696221451022157</v>
       </c>
       <c r="K19" t="n">
-        <v>21.79314969813606</v>
+        <v>16.05136879741746</v>
       </c>
       <c r="L19" t="n">
-        <v>43.35656929698318</v>
+        <v>43.95279505246828</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95191711047934</v>
+        <v>99.94067278306431</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.51868764295757</v>
+        <v>81.36578061991075</v>
       </c>
       <c r="C20" t="n">
-        <v>32.3359142221547</v>
+        <v>37.62927334024921</v>
       </c>
       <c r="D20" t="n">
-        <v>1.136237895627696</v>
+        <v>1.377976179653598</v>
       </c>
       <c r="E20" t="n">
-        <v>11.09879217109438</v>
+        <v>11.93510504851376</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7590057958216653</v>
+        <v>0.7518525947334839</v>
       </c>
       <c r="G20" t="n">
-        <v>19.35905498124446</v>
+        <v>23.5872338477752</v>
       </c>
       <c r="H20" t="n">
-        <v>37.21835990276971</v>
+        <v>37.52940185919302</v>
       </c>
       <c r="I20" t="n">
-        <v>1.203450672514269</v>
+        <v>1.485132372957419</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743786223885407</v>
+        <v>4.699078717084276</v>
       </c>
       <c r="K20" t="n">
-        <v>24.48131235704242</v>
+        <v>18.63421938008926</v>
       </c>
       <c r="L20" t="n">
-        <v>43.14267969590456</v>
+        <v>43.68703296829539</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95990627510167</v>
+        <v>99.95052568863386</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.61712766715202</v>
+        <v>78.7855807560404</v>
       </c>
       <c r="C21" t="n">
-        <v>36.1303417906137</v>
+        <v>35.27823619193867</v>
       </c>
       <c r="D21" t="n">
-        <v>1.137037611569071</v>
+        <v>1.28229467143058</v>
       </c>
       <c r="E21" t="n">
-        <v>13.14016958211364</v>
+        <v>11.31275247430664</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7595400052833016</v>
+        <v>0.7522464857636733</v>
       </c>
       <c r="G21" t="n">
-        <v>21.11902413453517</v>
+        <v>21.94942461515734</v>
       </c>
       <c r="H21" t="n">
-        <v>38.99089893328647</v>
+        <v>37.54906328599962</v>
       </c>
       <c r="I21" t="n">
-        <v>1.723332367343724</v>
+        <v>1.238258687359569</v>
       </c>
       <c r="J21" t="n">
-        <v>4.747125033020634</v>
+        <v>4.70154053602296</v>
       </c>
       <c r="K21" t="n">
-        <v>18.382872332848</v>
+        <v>21.2144192439596</v>
       </c>
       <c r="L21" t="n">
-        <v>45.42938186683759</v>
+        <v>43.46609088707514</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94259599029928</v>
+        <v>99.95874632297341</v>
       </c>
     </row>
   </sheetData>
